--- a/syllabuses.xlsx
+++ b/syllabuses.xlsx
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -475,7 +475,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_rus_b_beo_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_rus_b_beo_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_lit_b_iyy_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_lit_b_iyy_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_ist_b_riy_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_ist_b_riy_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_obsh_b_ean_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_obsh_b_ean_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -543,262 +543,364 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_pravo_b_nav_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_pravo_b_nav_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Д. В. Плотникова</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_eng_u_pdv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_eng_u_glr_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Е. В. Петрова</t>
+          <t>Д. В. Плотникова</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_eng_u_pev_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_eng_u_pdv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>У. Райс</t>
+          <t>Е. В. Петрова</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_eng_u_ru_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_eng_u_pev_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских</t>
+          <t>У. Райс</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_isp_b_1_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_eng_u_ru_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Китайский язык</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Н. Н. Шаталова</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_kit_b_shnn_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_isp_1_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>География</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Е. В. Бетехтин</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_geo_b_bev_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_isp_2_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>И. А. Нимерницкая</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_econ_b_nia_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_isp_4_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Биология</t>
+          <t>Немецкий язык (начинающие)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>В. В. Майчак</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_bio_b_mvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_nem_n_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Физика</t>
+          <t>Неизвестный предмет</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>А. А. Кочегаров</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_fiz_b_kaa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_9_10_2_kit_b_mds_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Химия</t>
+          <t>Неизвестный предмет</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Д. В. Ефанов</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_him_b_edv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_9_2_kit_b_mds_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>География</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>А. А. Коваленко</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_alg_b_kaa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_geo_b_evb_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>Экономика</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>А. А. Коваленко</t>
+          <t>И. А. Нимерницкиая</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_geom_b_kaa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_econ_b_nia_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Теория вероятности</t>
+          <t>Биология</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>А. А. Коваленко</t>
+          <t>В. В. Майчак</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_teorver_b_kaa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_bio_b_mvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Информатика</t>
+          <t>Физика</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Д.А. Панфилова, А.Ю. Величко</t>
+          <t>А. А. Коваленко</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_inf_b_pda_vay_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_fiz_b_kaa_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Химия</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Д. В. Ефанов</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_him_b_edv_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Алгебра</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>А. А. Коваленко</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_alg_b_kaa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Геометрия</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>А. А. Коваленко</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_geom_b_kaa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Теория вероятности</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>А. А. Коваленко</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_teorver_b_kaa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Информатика</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Д. А. Панфилова</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_inf_b_pda_kav_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Технология</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Д. А. Панфилова</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_8_1_tekn_b_pda_2025.pdf</t>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_2_tekn_b_pda_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Неизвестный предмет</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_8_9_10_2_kit_b_mds_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -813,12 +915,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -851,7 +953,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_rus_b_beo_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_rus_b_beo_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -868,7 +970,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_lit_b_iyy_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_lit_b_iyy_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -885,7 +987,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_ist_b_riy_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_ist_b_riy_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -902,7 +1004,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_obsh_b_ean_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_obsh_b_ean_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -919,7 +1021,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_pravo_b_nav_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_pravo_b_nav_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -936,7 +1038,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_tok_b_gsm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_ToK_b_gsm_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -948,12 +1050,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>У. Райс (1)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_eng_u_ru_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_eng_В1_kna_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -965,29 +1067,29 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>У. Райс (2)</t>
+          <t>В. В. Хитрук</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_eng_u_2_ru_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_eng_GWB1_hvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Д. В. Плотникова</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_eng_u_pdv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_eng_u_GWB1+_hvv_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -999,301 +1101,403 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>В. В. Хитрук (GWB1)</t>
+          <t>А. Л. Ромашкина</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_eng_u_GWB1_hvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_eng_Prepare!5_ral_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>В. В. Хитрук (GWB1+)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_eng_u_GWB1+_hvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_eng_u_glr_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Е. Петрова</t>
+          <t>Д. В. Плотникова</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_eng_u_pev_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_eng_u_pdv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (начинающие)</t>
+          <t>Е. В. Петрова</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_nem_n_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_eng_u_pev_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (продолжающие-1)</t>
+          <t>У. Райс</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_nem_p1_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_eng_u_ru_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Немецкий язык (начинающие)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (продолжающие-2)</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_nem_p2_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_nem_n_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Немецкий язык</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских (1)</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_isp_b_1_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_nem_p1_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Немецкий язык</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских (2)</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_isp_b_2_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_nem_p2_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>География</t>
+          <t>Немецкий язык</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Е. В. Бетехтин</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_geo_b_bev_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_nem_p3_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>И. А. Нимерницкая</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_econ_b_nia_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_isp_1_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Биология</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>В. В. Майчак</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_bio_b_mvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_isp_2_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Физика</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>В. Н. Белянин</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_fiz_b_bvn_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_isp_3_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Химия</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Д. В. Ефанов</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_him_b_edv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_isp_4_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>Неизвестный предмет</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>А. В. Пчелинцева</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_alg_b_pav_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_10_11_2_kit_b_mds_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>География</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>А. В. Пчелинцева</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_geom_b_pav_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_geo_b_evb_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Теория вероятности</t>
+          <t>Экономика</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>А. В. Пчелинцева</t>
+          <t>И. А. Нимерницкиая</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_teorver_b_pav_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_econ_b_nia_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Информатика</t>
+          <t>Биология</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Д.А. Панфилова, А.Ю. Величко</t>
+          <t>В. В. Майчак</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_inf_b_pda_vay_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_bio_b_mvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>Химия</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Д. В. Ефанов</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_him_b_edv_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Физика</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>В. Н. Белянин</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_fiz_b_bvn_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Алгебра</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_alg_b_naa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Геометрия</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_geom_b_naa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Теория вероятности</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_teorver_b_naa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Информатика</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Д. А. Панфилова</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_inf_b_pda_kav_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>Технология</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Д. А. Панфилова</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_9_1_tekn_b_pda_2025.pdf</t>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_9_2_tekn_b_pda_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1512,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1346,7 +1550,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_rus_b_pea_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_rus_b_pea_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -1358,29 +1562,29 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>П. Ф. Подковыркин (базовый)</t>
+          <t>П. Ф. Подковыркин</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_lit_b_ppf_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_lit_b_ppf_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Литература</t>
+          <t>Литература (углублённый)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>П. Ф. Подковыркин (углублённый)</t>
+          <t>П. Ф. Подковыркин</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_lit_u_ppf_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_lit_u_ppf_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -1397,14 +1601,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_ist_b_kan_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_ist_b_kan_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>История</t>
+          <t>История (углублённый)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1414,7 +1618,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_ist_u_gvk_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_ist_u_gvk_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1630,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>С. М. Гнездилов</t>
+          <t>А. Н. Егорова</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_obsh_b_gsm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_obsh_b_ean_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -1443,36 +1647,36 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>А. Н. Егорова</t>
+          <t>С. М. Гнездилов</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_obsh_b_ean_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_obsh_b_gsm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Право</t>
+          <t>Неизвестный предмет (углублённый)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>А. В. Юсупов</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_prav_u_uav_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_prav_u_yav_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Право</t>
+          <t>Неизвестный предмет (углублённый)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1482,568 +1686,738 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_prav_u_msn_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_prav_u_msn_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Теория и история искусства</t>
+          <t>Неизвестный предмет (углублённый)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Д. С. Матюнина</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_teor_isk_b_vkn_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_prav_u_yur_msn_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Теория познания</t>
+          <t>Политология (углублённый)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>И. С. Курилович</t>
+          <t>С. А. Кожеуров</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_ToK_u_kis_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_polit_u_ksa_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Социология (углублённый)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>С. С. Московская</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_eng_u_mss_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_soc_u_sma_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Неизвестный предмет</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Е. В. Петрова</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_eng_u_pev_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_teor_isk_b_vkn_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Теория познания</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Д. В. Плотникова</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_eng_u_pdv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_ToK_kis_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (начинающие)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_nem_n_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_eng_u_B1+_ral_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Английский язык</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (продолжающие-1)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_nem_p1_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_eng_Gateway_В2+_nia_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Английский язык</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (продолжающие-2)</t>
+          <t>И. А. Нимерницкиая</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_nem_p2_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_eng_Prepare_nia_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (продолжающие-3)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_nem_p3_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_eng_u_glr_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских (1)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_isp_b_1_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_eng_u_glr_2026+.pdf</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских (2)</t>
+          <t>С. С. Московская</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_isp_b_2_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_eng_u_mss_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских (3)</t>
+          <t>Д. В. Плотникова</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_isp_b_3_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_eng_u_pdv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских (4)</t>
+          <t>Е. В. Петрова</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_isp_b_4_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_eng_u_pev_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Итальянский язык</t>
+          <t>Немецкий язык (начинающие)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Е. С. Гурьева</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_ital_b_ges_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_nem_n_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Китайский язык</t>
+          <t>Немецкий язык</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Н. Н. Шаталова</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_kit_b_shnn_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_nem_p1_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Арабский язык</t>
+          <t>Немецкий язык</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Е. И. Смирнова</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_arab_b_sei_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_nem_p2_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>География</t>
+          <t>Немецкий язык</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Д. В. Степаньков</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_geo_b_sdv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_nem_p3_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>И. А. Нимерницкая (базовый)</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_econ_b_nia_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_isp_1_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>И. А. Нимерницкая (углублённый)</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_econ_u_nia_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_isp_2_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>М. И. Мозгачёв</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_econ_u_mmi_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_isp_3_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Биология</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>В. В. Майчак (базовый)</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_bio_b_mvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_isp_4_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Биология</t>
+          <t>Итальянский язык</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>В. В. Майчак (углублённый)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_bio_u_mvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_ital_ges_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Химия</t>
+          <t>Французский язык</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Д. В. Ефанов</t>
+          <t>М. С. Салкина</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_him_b_edv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_fr_b_sms_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Физика</t>
+          <t>Китайский язык (углублённый)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>А. А. Кочегаров</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_fiz_b_kaa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_kit_u_mds_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>Китайский язык (углублённый)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>А. М. Городнов (базовый)</t>
+          <t>Н. Н. Шаталова</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_alg_b_gam_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_kit_u_shnn_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>Арабский язык</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>В. К. Ушаков (углублённый)</t>
+          <t>Е. И. Смирнова</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_alg_u_uvk_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_arab_b_sei_2026_up.pdf</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>География</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>А. Ю. Величко (углублённый)</t>
+          <t>Д. В. Степаньков</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_alg_u_vay_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_geo_b_sdv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>Экономика (углублённый)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>А. А. Коваленко (базовый)</t>
+          <t>М. И. Мозгачёв</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_alg_b_kaa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_econ_u_mmi_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>Экономика</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>А. М. Городнов (базовый)</t>
+          <t>И. А. Нимерницкиая</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_geom_b_gam_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_econ_b_nia_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>Биология</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>В. К. Ушаков (углублённый)</t>
+          <t>В. В. Майчак</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_geom_u_uvk_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_bio_b_mvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>Биология (углублённый)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>А. Ю. Величко (углублённый)</t>
+          <t>В. В. Майчак</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_geom_u_vay_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_bio_u_mvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>Химия</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>А. А. Коваленко (базовый)</t>
+          <t>Д. В. Ефанов</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_geom_b_kaa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_him_b_edv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Информатика</t>
+          <t>Физика</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Д. А. Панфилова, А. Ю. Величко</t>
+          <t>А. А. Коваленко</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_10_1_inf_u_pda_vay_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_fiz_b_kaa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Алгебра</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>А. М. Городнов</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_alg_b_gam_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Алгебра</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>А. А. Коваленко</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_alg_b_kaa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Алгебра (углублённый)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_alg_u_kav_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Алгебра (углублённый)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>В. К. Ушаков</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_alg_u_uvk_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Геометрия</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>А. М. Городнов</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_geom_b_gam_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Геометрия</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>А. А. Коваленко</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_geom_b_kaa_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Геометрия (углублённый)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Требует уточнения</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_geom_u_kav_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Геометрия (углублённый)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>В. К. Ушаков</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_geom_u_uvk_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Информатика (углублённый)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Д. А. Панфилова</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_inf_u_pda_kav_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Китайский язык (углублённый)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Н. Н. Шаталова</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_10_2_kit_u_shnn_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -2091,12 +2465,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Е. В. Гаранина, Е. О. Борисова</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_rus_b_gev_beo_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_rus_b_gev_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -2108,352 +2482,352 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>А. С. Сенилова (базовый)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_lit_b_sas_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_lit_b_sas_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Литература</t>
+          <t>Литература (углублённый)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Е. В. Гаранина, Ю. Ю. Ишутин (углублённый)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_lit_u_gev_iyy_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_lit_u_gev_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Теория и история искусства</t>
+          <t>История</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Д. С. Матюнина</t>
+          <t>А. Н. Кадыков</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_teor_isk_b_mds_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_ist_b_kan_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>История</t>
+          <t>История (углублённый)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>А. Н. Кадыков (базовый)</t>
+          <t>А. Ф. Цветкова</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_ist_b_kan_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_ist_u_caf_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>История</t>
+          <t>Неизвестный предмет (углублённый)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>А. Ф. Цветкова (углублённый)</t>
+          <t>А. А. Атаманенко</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_ist_u_caf_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_vpinv_u_aaa_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Всеобщая политическая история</t>
+          <t>Неизвестный предмет (углублённый)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>А. А. Атаманенко</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_polist_u_aaa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_prav_u_yav_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Политология</t>
+          <t>Неизвестный предмет (углублённый)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>С. А. Кожеуров</t>
+          <t>С.Н. Мореева</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_polit_u_ksa_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_prav_u_msn_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Право</t>
+          <t>Обществознание (углублённый)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>А. В. Юсупов</t>
+          <t>А. Н. Егорова</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_prav_u_uav_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_obsh_u_ean_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Право</t>
+          <t>Обществознание</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>С.Н. Мореева (юридический)</t>
+          <t>А. Н. Егорова</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_prav_u_2_msn_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_obsh_b_ean_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Обществознание</t>
+          <t>Неизвестный предмет</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>А. Н. Егорова (базовый)</t>
+          <t>С. М. Гнездилов</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_obsh_b_ean_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_chio_b_gsm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Обществознание</t>
+          <t>Английский язык</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>А. Н. Егорова (углублённый)</t>
+          <t>У. Райс</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_obsh_u_ean_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_eng_В2_ru_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Социология</t>
+          <t>Английский язык</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>М. А. Серкина</t>
+          <t>У. Райс</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_soc_u_sma_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_eng_С1_ru_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>В. В. Хитрук (Gateway В2)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_eng_u_GWB2_hvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_eng_u_GWB2_hvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>В. В. Хитрук (Gateway С1)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_eng_u_GWC1_hvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_eng_u_GWC1_hvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>В. В. Хитрук (Prepare 7)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_eng_u_PR7_hvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_eng_u_PR7_hvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>С. С. Московская</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_eng_u_mss_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_eng_u_B2_ral_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык (углублённый)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>А. Л. Ромашкина</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_eng_u_ral_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_eng_u_1_ges_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык State Exam (углублённый)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Е. С. Гурина</t>
+          <t>С. С. Московская</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_eng_u_1_ges_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_state_u_mss_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Английский язык State Exam (углублённый)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>У. Райс</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_eng_u_ru_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_state_u_kna_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Английский язык State Exam</t>
+          <t>Немецкий язык</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Е. В. Петрова</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_state_u_pev_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_nem_p1_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Английский язык State Exam</t>
+          <t>Немецкий язык</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>С. С. Московская</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_state_u_mss_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_nem_p2_tob_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -2465,46 +2839,46 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (продолжающие-1)</t>
+          <t>О. Б. Темежникова</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_nem_p1_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_nem_p3_tob_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (продолжающие-2)</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_nem_p2_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_isp_3_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Немецкий язык</t>
+          <t>Испанский язык</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>О. Б. Темежникова (продолжающие-3)</t>
+          <t>М. М. Шустовских</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_nem_p3_tob_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_isp_4_shmm_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -2521,184 +2895,184 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_isp_b_lev_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_isp_b_lev_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Итальянский язык</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских (3)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_isp_b_3_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_ital_ges_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Испанский язык</t>
+          <t>Китайский язык (углублённый)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>М. М. Шустовских (4)</t>
+          <t>Требует уточнения</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_isp_b_4_shmm_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/Sil_11_2_kit_u_mds_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Итальянский язык</t>
+          <t>Арабский язык</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Е. С. Гурьева</t>
+          <t>Е. И. Смирнова</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_ital_b_ges_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_arab_b_sei_2026_up.pdf</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Французский язык</t>
+          <t>География</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>М. С. Салкина</t>
+          <t>Д. В. Степаньков</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_fr_b_sms_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_geo_b_sdv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Китайский язык</t>
+          <t>Экономика</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Н. Н. Шаталова</t>
+          <t>И. А. Нимерницкиая</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_kit_u_shnn_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_econ_b_nia_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Арабский язык</t>
+          <t>Экономика (углублённый)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Е. И. Смирнова</t>
+          <t>И. А. Нимерницкиая</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_arab_b_sei_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_econ_u_nia_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>География</t>
+          <t>Биология (углублённый)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Д. В. Степаньков</t>
+          <t>В. В. Майчак</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_geo_b_sdv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_bio_u_mvv_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>Алгебра (углублённый)</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>И. А. Нимерницкая (базовый)</t>
+          <t>В. С. Осипова</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_econ_b_nia_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_alg_u_ovs_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Экономика</t>
+          <t>Алгебра (углублённый)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>И. А. Нимерницкая (углублённый)</t>
+          <t>В. К. Ушаков</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_econ_u_nia_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_alg_u_uvk_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Биология</t>
+          <t>Алгебра (углублённый)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>В. В. Майчак</t>
+          <t>А. В. Пчелинцева</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_bio_u_mvv_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_alg_u_pav_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>Геометрия (углублённый)</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2708,14 +3082,14 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_alg_u_uvk_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_geom_u_uvk_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>Геометрия (углублённый)</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2725,109 +3099,58 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_alg_u_ovs_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_geom_u_ovs_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Алгебра</t>
+          <t>Геометрия (углублённый)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>А. В. Петров</t>
+          <t>А. В. Пчелинцева</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_alg_u_pav_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_geom_u_pav_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>Информатика</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>В. К. Ушаков</t>
+          <t>Ю. П. Мартемьянов</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_geom_u_uvk_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_inf_b_myp_2025.pdf</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Геометрия</t>
+          <t>Информатика (углублённый)</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>В. С. Осипова</t>
+          <t>Д. А. Панфилова</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_geom_u_ovs_2025.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Геометрия</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>А. В. Петров</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_geom_u_pav_2025.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Информатика</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Ю. П. Мартемьянов (базовый)</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_inf_b_myp_2025.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Информатика</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Д. А. Панфилова, А. Ю. Величко (углублённый)</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>https://ranepa-lyceum.ru/docs/sil_25-26_1/sil_11_1_inf_u_pda_vay_2025.pdf</t>
+          <t>https://ranepa-lyceum.ru/docs/sil_25-26_2/sil_11_2_inf_u_pda_kav_2026.pdf</t>
         </is>
       </c>
     </row>

--- a/syllabuses.xlsx
+++ b/syllabuses.xlsx
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>А. В. Пчелинцева</t>
+          <t>А. В. Петров</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>А. В. Пчелинцева</t>
+          <t>А. В. Петров</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
